--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -457,17 +457,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
+          <t>MONDRAGON HERNANDEZ WILMER JUNIOR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6">
@@ -487,17 +487,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MONDRAGON HERNANDEZ WILMER JUNIOR</t>
+          <t>CAMPOS PEREZ YOVERLY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -507,27 +507,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HUAYHUA VALDIVIA LUZ EXMILDA</t>
+          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAMPOS PEREZ YOVERLY</t>
+          <t>HUAYHUA VALDIVIA LUZ EXMILDA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -537,47 +537,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHAVEZ VILLANUEVA SILVIA JANETH</t>
+          <t>LOZADA ROJAS LUZ ELENA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LOZADA ROJAS LUZ ELENA</t>
+          <t>CHAVEZ VILLANUEVA SILVIA JANETH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOTO LOZANO LUZDINA</t>
+          <t>VASQUEZ SILVA ALOIS ADOLF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VASQUEZ SILVA ALOIS ADOLF</t>
+          <t>SOTO LOZANO LUZDINA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -467,37 +467,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PEREZ LINARES TATHIANA</t>
+          <t>LINARES PEREZ YANASELY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LINARES PEREZ YANASELY</t>
+          <t>CAMPOS PEREZ YOVERLY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAMPOS PEREZ YOVERLY</t>
+          <t>PEREZ LINARES TATHIANA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -563,21 +563,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VASQUEZ SILVA ALOIS ADOLF</t>
+          <t>SOTO LOZANO LUZDINA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOTO LOZANO LUZDINA</t>
+          <t>VASQUEZ SILVA ALOIS ADOLF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LINARES PEREZ YANASELY</t>
+          <t>CAMPOS PEREZ YOVERLY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAMPOS PEREZ YOVERLY</t>
+          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
@@ -497,43 +497,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MEDINA TAPIA ANA YULI</t>
+          <t>LINARES PEREZ YANASELY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
+          <t>MEDINA TAPIA ANA YULI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HUAYHUA VALDIVIA LUZ EXMILDA</t>
+          <t>DELGADO VASQUEZ FLOR MAGALY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DELGADO VASQUEZ FLOR MAGALY</t>
+          <t>HUAYHUA VALDIVIA LUZ EXMILDA</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">

--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -477,47 +477,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
+          <t>LINARES PEREZ YANASELY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PEREZ LINARES TATHIANA</t>
+          <t>MEDINA TAPIA ANA YULI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LINARES PEREZ YANASELY</t>
+          <t>INCIO SANCHEZ PAOLA KATHERINE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MEDINA TAPIA ANA YULI</t>
+          <t>PEREZ LINARES TATHIANA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -557,27 +557,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOTO LOZANO LUZDINA</t>
+          <t>VASQUEZ SILVA ALOIS ADOLF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VASQUEZ SILVA ALOIS ADOLF</t>
+          <t>SOTO LOZANO LUZDINA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -447,27 +447,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TANTALEAN BUSTAMANTE ESTALIN YOEL</t>
+          <t>MONDRAGON HERNANDEZ WILMER JUNIOR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MONDRAGON HERNANDEZ WILMER JUNIOR</t>
+          <t>TANTALEAN BUSTAMANTE ESTALIN YOEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DELGADO VASQUEZ FLOR MAGALY</t>
+          <t>LOZADA ROJAS LUZ ELENA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -537,37 +537,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOZADA ROJAS LUZ ELENA</t>
+          <t>DELGADO VASQUEZ FLOR MAGALY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHAVEZ VILLANUEVA SILVIA JANETH</t>
+          <t>VASQUEZ SILVA ALOIS ADOLF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VASQUEZ SILVA ALOIS ADOLF</t>
+          <t>CHAVEZ VILLANUEVA SILVIA JANETH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_huambocancha_alta.xlsx
+++ b/data/data_monitoreo_huambocancha_alta.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
